--- a/DATA/MINI SPLIT SCHEDULE.xlsx
+++ b/DATA/MINI SPLIT SCHEDULE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericc\Documents\HHpro\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProgramData\HHpro\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE901398-C6FC-47C6-A100-28EC785C1B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11DABAA-2416-44C7-86F3-6461F523FEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{096B7824-FEFC-479B-B7FF-F552B63F2E04}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>MAX ALLOWABLE LINE-SET LENGTHS</t>
   </si>
   <si>
-    <t>ACCESSORIES</t>
-  </si>
-  <si>
     <t>SYMBOL</t>
   </si>
   <si>
@@ -116,12 +113,6 @@
     <t>SYMBOL (OUTDOOR UNIT)</t>
   </si>
   <si>
-    <t>ACCESSORIES (INDOOR UNIT):</t>
-  </si>
-  <si>
-    <t>ACCESSORIES (OUTDOOR UNIT):</t>
-  </si>
-  <si>
     <t>1-</t>
   </si>
   <si>
@@ -150,6 +141,15 @@
   </si>
   <si>
     <t>10-</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>NOTES (INDOOR UNIT):</t>
+  </si>
+  <si>
+    <t>NOTES (OUTDOOR UNIT):</t>
   </si>
 </sst>
 </file>
@@ -571,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -607,21 +607,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -631,34 +646,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1013,24 +1012,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="32"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="37"/>
     </row>
     <row r="2" spans="2:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="27" t="s">
@@ -1053,80 +1052,80 @@
       <c r="Q2" s="29"/>
     </row>
     <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="40" t="s">
+      <c r="E3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="37" t="s">
+      <c r="J3" s="32"/>
+      <c r="K3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="39"/>
-      <c r="K3" s="35" t="s">
+      <c r="L3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="33" t="s">
+      <c r="M3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="N3" s="31"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="38"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="25" t="s">
-        <v>4</v>
+      <c r="Q3" s="33" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="26"/>
-      <c r="C4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="41"/>
       <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="39"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="36"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="26"/>
+      <c r="Q4" s="34"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="6"/>
@@ -1545,60 +1544,60 @@
       <c r="Q27" s="5"/>
     </row>
     <row r="28" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="33" t="s">
+      <c r="B28" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="E28" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="37" t="s">
+      <c r="G28" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="31"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="K28" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="L28" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="M28" s="33" t="s">
-        <v>4</v>
+      <c r="M28" s="25" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="26"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
       <c r="G29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="K29" s="41"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="6"/>
@@ -1910,7 +1909,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B52" s="23" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -1919,7 +1918,7 @@
       <c r="G52" s="17"/>
       <c r="H52" s="18"/>
       <c r="I52" s="23" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J52" s="17"/>
       <c r="K52" s="17"/>
@@ -1928,182 +1927,102 @@
     </row>
     <row r="53" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B53" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
+        <v>25</v>
+      </c>
       <c r="H53" s="19"/>
       <c r="I53" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="J53" s="42"/>
-      <c r="K53" s="42"/>
-      <c r="L53" s="42"/>
+        <v>25</v>
+      </c>
       <c r="M53" s="19"/>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B54" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
+        <v>26</v>
+      </c>
       <c r="H54" s="19"/>
       <c r="I54" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="J54" s="42"/>
-      <c r="K54" s="42"/>
-      <c r="L54" s="42"/>
+        <v>26</v>
+      </c>
       <c r="M54" s="19"/>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
+        <v>27</v>
+      </c>
       <c r="H55" s="19"/>
       <c r="I55" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J55" s="42"/>
-      <c r="K55" s="42"/>
-      <c r="L55" s="42"/>
+        <v>27</v>
+      </c>
       <c r="M55" s="19"/>
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
+        <v>28</v>
+      </c>
       <c r="H56" s="19"/>
       <c r="I56" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
-      <c r="L56" s="42"/>
+        <v>28</v>
+      </c>
       <c r="M56" s="19"/>
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
+        <v>29</v>
+      </c>
       <c r="H57" s="19"/>
       <c r="I57" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="J57" s="42"/>
-      <c r="K57" s="42"/>
-      <c r="L57" s="42"/>
+        <v>29</v>
+      </c>
       <c r="M57" s="19"/>
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
+        <v>30</v>
+      </c>
       <c r="H58" s="19"/>
       <c r="I58" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="J58" s="42"/>
-      <c r="K58" s="42"/>
-      <c r="L58" s="42"/>
+        <v>30</v>
+      </c>
       <c r="M58" s="19"/>
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
+        <v>31</v>
+      </c>
       <c r="H59" s="19"/>
       <c r="I59" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="J59" s="42"/>
-      <c r="K59" s="42"/>
-      <c r="L59" s="42"/>
+        <v>31</v>
+      </c>
       <c r="M59" s="19"/>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
+        <v>32</v>
+      </c>
       <c r="H60" s="19"/>
       <c r="I60" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="J60" s="42"/>
-      <c r="K60" s="42"/>
-      <c r="L60" s="42"/>
+        <v>32</v>
+      </c>
       <c r="M60" s="19"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B61" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C61" s="42"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
+        <v>33</v>
+      </c>
       <c r="H61" s="19"/>
       <c r="I61" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="J61" s="42"/>
-      <c r="K61" s="42"/>
-      <c r="L61" s="42"/>
+        <v>33</v>
+      </c>
       <c r="M61" s="19"/>
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" s="42"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="42"/>
+        <v>34</v>
+      </c>
       <c r="H62" s="19"/>
       <c r="I62" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
-      <c r="L62" s="42"/>
+        <v>34</v>
+      </c>
       <c r="M62" s="19"/>
     </row>
     <row r="63" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2122,11 +2041,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:I28"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B1:Q1"/>
@@ -2143,6 +2057,11 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K28:K29"/>
     <mergeCell ref="L28:L29"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:I28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
